--- a/data/trans_camb/IP2003-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-1.049691518382287</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-5.105778285067212</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.254082751400889</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.772518608767268</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.02634576505943786</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.4875777323001762</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-5.930266191045988</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-10.96363840050899</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.321280841542316</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.610664303897315</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.833514749088406</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-5.742281874415331</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>3.854671301593669</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.800175872857747</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.102517430966675</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>15.9205395141583</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>3.541336415195499</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>5.870366851704921</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.07320066653709545</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.3560535329784701</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.08169579158012501</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.3109002855980452</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.00177637981582234</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.03287523593824007</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.351452520480674</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.7012718005828363</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.2311614042718911</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.2237862071370616</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2295735955940797</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3691343067436495</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.3447100255625274</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.3510307807947297</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.6099295883097371</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.191015940312097</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2781936239340261</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.438870360661737</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.371115759660626</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.06386869805977968</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.649339032722574</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-4.894859810830654</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-3.002021080693937</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-2.326434795504065</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-7.106558598174321</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.784831290295737</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-10.57059167069287</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-10.99490523235496</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-7.518369461486047</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-7.243979143835198</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>5.050618591790368</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.59613348980619</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.996357443369178</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.859995388527072</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.209771433906036</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4.778936950225823</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.08486926130625831</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.00395334178513681</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.257660358419835</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.2712668025276118</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1755824944683585</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1360687395699986</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.3710868033381756</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.3978849584542201</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.4997308302564863</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.5309060003667706</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3803327420227046</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3863453543870702</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.4009641574671682</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.8988280888196836</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.155600548085054</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.1200688430316251</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.08470061391019718</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.3389908671039339</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.599951513536899</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.339455104543269</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-10.00503109641833</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-5.240056819218747</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-5.749292016203513</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-1.841891632154961</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-7.561107156435224</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.171108826483421</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-16.41602898173798</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-11.69843471262164</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-10.26409823683641</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-6.188006491943061</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>4.560585973096506</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.154562158184759</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-3.695466076924388</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.9130505444926619</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-1.661536339237715</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.858269209785794</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.1407144076142517</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.1178039646620484</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.5770588487116152</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.3022300606706067</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.402753165335249</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1290293975265457</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.536532474440143</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.304394854839019</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.7647268817171601</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.5518478129665946</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6104143914737841</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.3638953207564459</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.5898008708565395</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.8641294767081009</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-0.2263937725357633</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.07397028045463419</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.1263516678154074</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.2488872244141838</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>4.097945898236353</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4.959961825827201</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.539215366205717</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.276871506823316</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>2.453063482226711</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>3.352313372453933</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-3.818651419137708</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-2.4889450574151</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-9.502448464371845</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-8.280172149887774</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-3.714152975213759</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-2.177053226107905</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>12.26123511169469</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>11.7586542607249</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>10.1158027078966</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>8.693226571866772</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8.66203807996815</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>8.852078754922911</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.4553393545266028</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.551121433111338</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.03695635919649867</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.08751331102818383</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.2124605582843834</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.2903448589146387</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.3411219175520148</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.2219645968044546</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.4953882449639915</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.3790977227189897</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.2556730734927687</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.1578791227744345</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>2.095219271458602</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2.106365915326795</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1.116143649413683</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.9022248504713776</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.058289559161013</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.020180316646145</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.5433123552991137</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.03042391621776996</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-3.068597858636327</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-2.118195012326105</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.772926449803045</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-1.029301121630072</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.404845077343953</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-3.439185197857337</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-6.542646863546735</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-5.672320243973751</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-3.991593421920884</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-3.527005198705788</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>2.379774555963397</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>4.6915313708688</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.4003605115681627</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.579225185255499</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.4150369702684724</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.733270786395329</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.04015077280881598</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.002248326834646763</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.1852835000636502</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.1278976926209412</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1181533252782589</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.0685958237279076</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.2323029724035888</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.2338824472642058</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.3501901297791212</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.3119215293468568</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.2438530052972909</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.2264791325622671</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.1941039090520306</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.3882084288350962</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.03589643477648811</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.1070459947203079</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.02195981420362169</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.1247116079365142</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
